--- a/Team-Data/2013-14/1-14-2013-14.xlsx
+++ b/Team-Data/2013-14/1-14-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>1.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE2" t="n">
         <v>11</v>
@@ -754,7 +821,7 @@
         <v>7</v>
       </c>
       <c r="AI2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ2" t="n">
         <v>18</v>
@@ -769,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="AN2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO2" t="n">
         <v>19</v>
       </c>
       <c r="AP2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ2" t="n">
         <v>9</v>
@@ -793,22 +860,22 @@
         <v>1</v>
       </c>
       <c r="AV2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW2" t="n">
         <v>7</v>
       </c>
       <c r="AX2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ2" t="n">
         <v>5</v>
       </c>
       <c r="BA2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB2" t="n">
         <v>14</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-14-2013-14</t>
+          <t>2014-01-14</t>
         </is>
       </c>
     </row>
@@ -924,7 +991,7 @@
         <v>1</v>
       </c>
       <c r="AE3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF3" t="n">
         <v>27</v>
@@ -954,7 +1021,7 @@
         <v>26</v>
       </c>
       <c r="AO3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AP3" t="n">
         <v>26</v>
@@ -969,10 +1036,10 @@
         <v>20</v>
       </c>
       <c r="AT3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU3" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AV3" t="n">
         <v>26</v>
@@ -984,7 +1051,7 @@
         <v>17</v>
       </c>
       <c r="AY3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ3" t="n">
         <v>23</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-14-2013-14</t>
+          <t>2014-01-14</t>
         </is>
       </c>
     </row>
@@ -1103,16 +1170,16 @@
         <v>-4.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AE4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF4" t="n">
         <v>18</v>
       </c>
       <c r="AG4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH4" t="n">
         <v>6</v>
@@ -1133,7 +1200,7 @@
         <v>19</v>
       </c>
       <c r="AN4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO4" t="n">
         <v>6</v>
@@ -1145,7 +1212,7 @@
         <v>15</v>
       </c>
       <c r="AR4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS4" t="n">
         <v>25</v>
@@ -1166,10 +1233,10 @@
         <v>28</v>
       </c>
       <c r="AY4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA4" t="n">
         <v>6</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-14-2013-14</t>
+          <t>2014-01-14</t>
         </is>
       </c>
     </row>
@@ -1207,97 +1274,97 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F5" t="n">
         <v>23</v>
       </c>
       <c r="G5" t="n">
-        <v>0.41</v>
+        <v>0.395</v>
       </c>
       <c r="H5" t="n">
         <v>48.4</v>
       </c>
       <c r="I5" t="n">
-        <v>34.9</v>
+        <v>34.8</v>
       </c>
       <c r="J5" t="n">
-        <v>81.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.427</v>
+        <v>0.425</v>
       </c>
       <c r="L5" t="n">
         <v>5.3</v>
       </c>
       <c r="M5" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="N5" t="n">
-        <v>0.341</v>
+        <v>0.339</v>
       </c>
       <c r="O5" t="n">
-        <v>18.3</v>
+        <v>18.1</v>
       </c>
       <c r="P5" t="n">
-        <v>25.1</v>
+        <v>24.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.73</v>
+        <v>0.728</v>
       </c>
       <c r="R5" t="n">
-        <v>9.699999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="S5" t="n">
         <v>32.5</v>
       </c>
       <c r="T5" t="n">
-        <v>42.2</v>
+        <v>42.3</v>
       </c>
       <c r="U5" t="n">
         <v>19.4</v>
       </c>
       <c r="V5" t="n">
-        <v>12.8</v>
+        <v>13</v>
       </c>
       <c r="W5" t="n">
         <v>6.4</v>
       </c>
       <c r="X5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Z5" t="n">
         <v>18.8</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="AB5" t="n">
-        <v>93.40000000000001</v>
+        <v>93</v>
       </c>
       <c r="AC5" t="n">
-        <v>-3.2</v>
+        <v>-3.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AE5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AG5" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AH5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI5" t="n">
         <v>27</v>
@@ -1318,13 +1385,13 @@
         <v>25</v>
       </c>
       <c r="AO5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ5" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AR5" t="n">
         <v>23</v>
@@ -1333,10 +1400,10 @@
         <v>13</v>
       </c>
       <c r="AT5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AV5" t="n">
         <v>2</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-14-2013-14</t>
+          <t>2014-01-14</t>
         </is>
       </c>
     </row>
@@ -1467,16 +1534,16 @@
         <v>-0.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF6" t="n">
         <v>14</v>
       </c>
       <c r="AG6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH6" t="n">
         <v>8</v>
@@ -1518,7 +1585,7 @@
         <v>9</v>
       </c>
       <c r="AU6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AV6" t="n">
         <v>27</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-14-2013-14</t>
+          <t>2014-01-14</t>
         </is>
       </c>
     </row>
@@ -1571,61 +1638,61 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F7" t="n">
         <v>24</v>
       </c>
       <c r="G7" t="n">
-        <v>0.368</v>
+        <v>0.351</v>
       </c>
       <c r="H7" t="n">
         <v>49.1</v>
       </c>
       <c r="I7" t="n">
-        <v>36.4</v>
+        <v>36.3</v>
       </c>
       <c r="J7" t="n">
-        <v>85.59999999999999</v>
+        <v>85.5</v>
       </c>
       <c r="K7" t="n">
-        <v>0.425</v>
+        <v>0.424</v>
       </c>
       <c r="L7" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="M7" t="n">
         <v>19.8</v>
       </c>
       <c r="N7" t="n">
-        <v>0.37</v>
+        <v>0.361</v>
       </c>
       <c r="O7" t="n">
-        <v>16.1</v>
+        <v>15.8</v>
       </c>
       <c r="P7" t="n">
-        <v>21.6</v>
+        <v>21.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.745</v>
+        <v>0.743</v>
       </c>
       <c r="R7" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="S7" t="n">
-        <v>32.4</v>
+        <v>32.5</v>
       </c>
       <c r="T7" t="n">
         <v>44.4</v>
       </c>
       <c r="U7" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="V7" t="n">
-        <v>15.1</v>
+        <v>15.3</v>
       </c>
       <c r="W7" t="n">
         <v>7.1</v>
@@ -1643,22 +1710,22 @@
         <v>19.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>96.2</v>
+        <v>95.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>-5.5</v>
+        <v>-5.7</v>
       </c>
       <c r="AD7" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AF7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG7" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AH7" t="n">
         <v>1</v>
@@ -1673,16 +1740,16 @@
         <v>28</v>
       </c>
       <c r="AL7" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AM7" t="n">
         <v>24</v>
       </c>
       <c r="AN7" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AO7" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AP7" t="n">
         <v>20</v>
@@ -1700,16 +1767,16 @@
         <v>11</v>
       </c>
       <c r="AU7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AV7" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AW7" t="n">
         <v>23</v>
       </c>
       <c r="AX7" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AY7" t="n">
         <v>28</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-14-2013-14</t>
+          <t>2014-01-14</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1931,7 @@
         <v>6</v>
       </c>
       <c r="AO8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP8" t="n">
         <v>27</v>
@@ -1891,7 +1958,7 @@
         <v>1</v>
       </c>
       <c r="AX8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY8" t="n">
         <v>4</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-14-2013-14</t>
+          <t>2014-01-14</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>1</v>
       </c>
       <c r="AD9" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AE9" t="n">
         <v>12</v>
@@ -2049,10 +2116,10 @@
         <v>8</v>
       </c>
       <c r="AP9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AQ9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR9" t="n">
         <v>5</v>
@@ -2064,7 +2131,7 @@
         <v>4</v>
       </c>
       <c r="AU9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AV9" t="n">
         <v>13</v>
@@ -2079,7 +2146,7 @@
         <v>22</v>
       </c>
       <c r="AZ9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-14-2013-14</t>
+          <t>2014-01-14</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-3.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE10" t="n">
         <v>18</v>
@@ -2231,7 +2298,7 @@
         <v>17</v>
       </c>
       <c r="AP10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AQ10" t="n">
         <v>30</v>
@@ -2249,7 +2316,7 @@
         <v>18</v>
       </c>
       <c r="AV10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW10" t="n">
         <v>5</v>
@@ -2267,7 +2334,7 @@
         <v>13</v>
       </c>
       <c r="BB10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BC10" t="n">
         <v>21</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-14-2013-14</t>
+          <t>2014-01-14</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2456,7 @@
         <v>7</v>
       </c>
       <c r="AH11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI11" t="n">
         <v>5</v>
@@ -2416,7 +2483,7 @@
         <v>19</v>
       </c>
       <c r="AQ11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AR11" t="n">
         <v>16</v>
@@ -2440,10 +2507,10 @@
         <v>11</v>
       </c>
       <c r="AY11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BA11" t="n">
         <v>19</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-14-2013-14</t>
+          <t>2014-01-14</t>
         </is>
       </c>
     </row>
@@ -2571,7 +2638,7 @@
         <v>7</v>
       </c>
       <c r="AH12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI12" t="n">
         <v>18</v>
@@ -2589,7 +2656,7 @@
         <v>3</v>
       </c>
       <c r="AN12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO12" t="n">
         <v>1</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-14-2013-14</t>
+          <t>2014-01-14</t>
         </is>
       </c>
     </row>
@@ -2663,40 +2730,40 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E13" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F13" t="n">
         <v>7</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.806</v>
       </c>
       <c r="H13" t="n">
         <v>48.1</v>
       </c>
       <c r="I13" t="n">
-        <v>36.2</v>
+        <v>35.9</v>
       </c>
       <c r="J13" t="n">
-        <v>79.40000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="K13" t="n">
-        <v>0.456</v>
+        <v>0.453</v>
       </c>
       <c r="L13" t="n">
         <v>7.1</v>
       </c>
       <c r="M13" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="N13" t="n">
-        <v>0.358</v>
+        <v>0.357</v>
       </c>
       <c r="O13" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="P13" t="n">
         <v>22.8</v>
@@ -2714,7 +2781,7 @@
         <v>44.6</v>
       </c>
       <c r="U13" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="V13" t="n">
         <v>15.8</v>
@@ -2723,28 +2790,28 @@
         <v>7.4</v>
       </c>
       <c r="X13" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Y13" t="n">
         <v>4.6</v>
       </c>
       <c r="Z13" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AA13" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>97.40000000000001</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AC13" t="n">
-        <v>9.300000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="AD13" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="AE13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF13" t="n">
         <v>1</v>
@@ -2756,13 +2823,13 @@
         <v>25</v>
       </c>
       <c r="AI13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ13" t="n">
         <v>27</v>
       </c>
       <c r="AK13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AL13" t="n">
         <v>21</v>
@@ -2771,19 +2838,19 @@
         <v>22</v>
       </c>
       <c r="AN13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO13" t="n">
         <v>13</v>
       </c>
       <c r="AP13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ13" t="n">
         <v>5</v>
       </c>
       <c r="AR13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS13" t="n">
         <v>3</v>
@@ -2795,19 +2862,19 @@
         <v>17</v>
       </c>
       <c r="AV13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW13" t="n">
         <v>18</v>
       </c>
       <c r="AX13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA13" t="n">
         <v>7</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-14-2013-14</t>
+          <t>2014-01-14</t>
         </is>
       </c>
     </row>
@@ -2935,7 +3002,7 @@
         <v>6</v>
       </c>
       <c r="AH14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI14" t="n">
         <v>11</v>
@@ -2944,13 +3011,13 @@
         <v>20</v>
       </c>
       <c r="AK14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL14" t="n">
         <v>12</v>
       </c>
       <c r="AM14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AN14" t="n">
         <v>27</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-14-2013-14</t>
+          <t>2014-01-14</t>
         </is>
       </c>
     </row>
@@ -3027,34 +3094,34 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E15" t="n">
         <v>14</v>
       </c>
       <c r="F15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G15" t="n">
-        <v>0.368</v>
+        <v>0.378</v>
       </c>
       <c r="H15" t="n">
         <v>48</v>
       </c>
       <c r="I15" t="n">
-        <v>36.7</v>
+        <v>36.5</v>
       </c>
       <c r="J15" t="n">
         <v>83.90000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>0.438</v>
+        <v>0.436</v>
       </c>
       <c r="L15" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="M15" t="n">
-        <v>25.3</v>
+        <v>25.1</v>
       </c>
       <c r="N15" t="n">
         <v>0.361</v>
@@ -3069,28 +3136,28 @@
         <v>0.747</v>
       </c>
       <c r="R15" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="S15" t="n">
-        <v>32.8</v>
+        <v>32.9</v>
       </c>
       <c r="T15" t="n">
-        <v>43</v>
+        <v>43.2</v>
       </c>
       <c r="U15" t="n">
-        <v>22.4</v>
+        <v>22.1</v>
       </c>
       <c r="V15" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="W15" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="X15" t="n">
         <v>5.8</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Z15" t="n">
         <v>20.7</v>
@@ -3099,19 +3166,19 @@
         <v>19.2</v>
       </c>
       <c r="AB15" t="n">
-        <v>99.8</v>
+        <v>99.3</v>
       </c>
       <c r="AC15" t="n">
-        <v>-5.7</v>
+        <v>-5.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE15" t="n">
         <v>23</v>
       </c>
       <c r="AF15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG15" t="n">
         <v>23</v>
@@ -3126,7 +3193,7 @@
         <v>11</v>
       </c>
       <c r="AK15" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AL15" t="n">
         <v>5</v>
@@ -3153,31 +3220,31 @@
         <v>11</v>
       </c>
       <c r="AT15" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AU15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW15" t="n">
         <v>28</v>
       </c>
       <c r="AX15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY15" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AZ15" t="n">
         <v>16</v>
       </c>
       <c r="BA15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC15" t="n">
         <v>26</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-14-2013-14</t>
+          <t>2014-01-14</t>
         </is>
       </c>
     </row>
@@ -3209,28 +3276,28 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F16" t="n">
         <v>19</v>
       </c>
       <c r="G16" t="n">
-        <v>0.486</v>
+        <v>0.472</v>
       </c>
       <c r="H16" t="n">
         <v>48.4</v>
       </c>
       <c r="I16" t="n">
-        <v>37.8</v>
+        <v>37.9</v>
       </c>
       <c r="J16" t="n">
-        <v>83.2</v>
+        <v>83.3</v>
       </c>
       <c r="K16" t="n">
-        <v>0.454</v>
+        <v>0.455</v>
       </c>
       <c r="L16" t="n">
         <v>5</v>
@@ -3239,34 +3306,34 @@
         <v>14.2</v>
       </c>
       <c r="N16" t="n">
-        <v>0.35</v>
+        <v>0.352</v>
       </c>
       <c r="O16" t="n">
-        <v>16</v>
+        <v>15.8</v>
       </c>
       <c r="P16" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.752</v>
+        <v>0.75</v>
       </c>
       <c r="R16" t="n">
         <v>12.3</v>
       </c>
       <c r="S16" t="n">
-        <v>31</v>
+        <v>30.9</v>
       </c>
       <c r="T16" t="n">
-        <v>43.2</v>
+        <v>43.3</v>
       </c>
       <c r="U16" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="V16" t="n">
         <v>13.5</v>
       </c>
       <c r="W16" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X16" t="n">
         <v>4.2</v>
@@ -3275,40 +3342,40 @@
         <v>5.7</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="AA16" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>96.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AC16" t="n">
-        <v>-0.8</v>
+        <v>-0.9</v>
       </c>
       <c r="AD16" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="AE16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF16" t="n">
         <v>14</v>
       </c>
       <c r="AG16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH16" t="n">
         <v>14</v>
       </c>
       <c r="AI16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ16" t="n">
         <v>14</v>
       </c>
       <c r="AK16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AL16" t="n">
         <v>30</v>
@@ -3320,13 +3387,13 @@
         <v>18</v>
       </c>
       <c r="AO16" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AP16" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AQ16" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AR16" t="n">
         <v>6</v>
@@ -3353,10 +3420,10 @@
         <v>21</v>
       </c>
       <c r="AZ16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA16" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BB16" t="n">
         <v>21</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-14-2013-14</t>
+          <t>2014-01-14</t>
         </is>
       </c>
     </row>
@@ -3469,13 +3536,13 @@
         <v>6.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AE17" t="n">
         <v>5</v>
       </c>
       <c r="AF17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG17" t="n">
         <v>5</v>
@@ -3502,7 +3569,7 @@
         <v>7</v>
       </c>
       <c r="AO17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP17" t="n">
         <v>11</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-14-2013-14</t>
+          <t>2014-01-14</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-8.800000000000001</v>
       </c>
       <c r="AD18" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3675,7 +3742,7 @@
         <v>30</v>
       </c>
       <c r="AL18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM18" t="n">
         <v>18</v>
@@ -3708,7 +3775,7 @@
         <v>24</v>
       </c>
       <c r="AW18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX18" t="n">
         <v>7</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-14-2013-14</t>
+          <t>2014-01-14</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>4.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AE19" t="n">
         <v>14</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-14-2013-14</t>
+          <t>2014-01-14</t>
         </is>
       </c>
     </row>
@@ -4015,16 +4082,16 @@
         <v>-1.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AE20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF20" t="n">
         <v>18</v>
       </c>
       <c r="AG20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH20" t="n">
         <v>9</v>
@@ -4063,16 +4130,16 @@
         <v>24</v>
       </c>
       <c r="AT20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV20" t="n">
         <v>4</v>
       </c>
       <c r="AW20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX20" t="n">
         <v>2</v>
@@ -4090,7 +4157,7 @@
         <v>15</v>
       </c>
       <c r="BC20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-14-2013-14</t>
+          <t>2014-01-14</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E21" t="n">
         <v>15</v>
       </c>
       <c r="F21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G21" t="n">
-        <v>0.395</v>
+        <v>0.405</v>
       </c>
       <c r="H21" t="n">
         <v>48.5</v>
@@ -4137,16 +4204,16 @@
         <v>36.3</v>
       </c>
       <c r="J21" t="n">
-        <v>83</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>0.438</v>
+        <v>0.437</v>
       </c>
       <c r="L21" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="M21" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="N21" t="n">
         <v>0.357</v>
@@ -4161,25 +4228,25 @@
         <v>0.762</v>
       </c>
       <c r="R21" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="S21" t="n">
         <v>29.3</v>
       </c>
       <c r="T21" t="n">
-        <v>39.7</v>
+        <v>39.9</v>
       </c>
       <c r="U21" t="n">
         <v>20.4</v>
       </c>
       <c r="V21" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="W21" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="X21" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Y21" t="n">
         <v>3.8</v>
@@ -4194,28 +4261,28 @@
         <v>95.40000000000001</v>
       </c>
       <c r="AC21" t="n">
-        <v>-2.8</v>
+        <v>-2.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF21" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI21" t="n">
         <v>21</v>
       </c>
-      <c r="AG21" t="n">
-        <v>22</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>11</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>22</v>
-      </c>
       <c r="AJ21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK21" t="n">
         <v>23</v>
@@ -4224,7 +4291,7 @@
         <v>8</v>
       </c>
       <c r="AM21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AN21" t="n">
         <v>15</v>
@@ -4248,16 +4315,16 @@
         <v>29</v>
       </c>
       <c r="AU21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV21" t="n">
         <v>1</v>
       </c>
       <c r="AW21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX21" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AY21" t="n">
         <v>5</v>
@@ -4266,7 +4333,7 @@
         <v>29</v>
       </c>
       <c r="BA21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB21" t="n">
         <v>24</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-14-2013-14</t>
+          <t>2014-01-14</t>
         </is>
       </c>
     </row>
@@ -4301,43 +4368,43 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E22" t="n">
         <v>28</v>
       </c>
       <c r="F22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G22" t="n">
-        <v>0.737</v>
+        <v>0.757</v>
       </c>
       <c r="H22" t="n">
         <v>48.3</v>
       </c>
       <c r="I22" t="n">
-        <v>38.4</v>
+        <v>38.6</v>
       </c>
       <c r="J22" t="n">
         <v>82.90000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>0.463</v>
+        <v>0.465</v>
       </c>
       <c r="L22" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="M22" t="n">
         <v>20.2</v>
       </c>
       <c r="N22" t="n">
-        <v>0.342</v>
+        <v>0.345</v>
       </c>
       <c r="O22" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="P22" t="n">
-        <v>25.7</v>
+        <v>25.8</v>
       </c>
       <c r="Q22" t="n">
         <v>0.8169999999999999</v>
@@ -4349,16 +4416,16 @@
         <v>35.9</v>
       </c>
       <c r="T22" t="n">
-        <v>46.9</v>
+        <v>47</v>
       </c>
       <c r="U22" t="n">
-        <v>21.5</v>
+        <v>21.8</v>
       </c>
       <c r="V22" t="n">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
       <c r="W22" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="X22" t="n">
         <v>6.2</v>
@@ -4367,31 +4434,31 @@
         <v>4</v>
       </c>
       <c r="Z22" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="AA22" t="n">
         <v>20.9</v>
       </c>
       <c r="AB22" t="n">
-        <v>104.7</v>
+        <v>105.2</v>
       </c>
       <c r="AC22" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE22" t="n">
         <v>3</v>
       </c>
       <c r="AF22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH22" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI22" t="n">
         <v>9</v>
@@ -4400,16 +4467,16 @@
         <v>17</v>
       </c>
       <c r="AK22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM22" t="n">
         <v>20</v>
       </c>
       <c r="AN22" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AO22" t="n">
         <v>3</v>
@@ -4430,13 +4497,13 @@
         <v>1</v>
       </c>
       <c r="AU22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AV22" t="n">
         <v>23</v>
       </c>
       <c r="AW22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX22" t="n">
         <v>1</v>
@@ -4445,7 +4512,7 @@
         <v>7</v>
       </c>
       <c r="AZ22" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="BA22" t="n">
         <v>12</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-14-2013-14</t>
+          <t>2014-01-14</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>-6.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE23" t="n">
         <v>29</v>
@@ -4573,34 +4640,34 @@
         <v>29</v>
       </c>
       <c r="AH23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ23" t="n">
         <v>22</v>
       </c>
       <c r="AK23" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AL23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM23" t="n">
         <v>15</v>
       </c>
       <c r="AN23" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO23" t="n">
         <v>23</v>
       </c>
-      <c r="AO23" t="n">
-        <v>25</v>
-      </c>
       <c r="AP23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR23" t="n">
         <v>27</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-14-2013-14</t>
+          <t>2014-01-14</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-8.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AE24" t="n">
         <v>28</v>
@@ -4767,7 +4834,7 @@
         <v>18</v>
       </c>
       <c r="AL24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM24" t="n">
         <v>11</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-14-2013-14</t>
+          <t>2014-01-14</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>2.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AE25" t="n">
         <v>10</v>
@@ -4955,7 +5022,7 @@
         <v>1</v>
       </c>
       <c r="AN25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO25" t="n">
         <v>14</v>
@@ -4964,13 +5031,13 @@
         <v>13</v>
       </c>
       <c r="AQ25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR25" t="n">
         <v>11</v>
       </c>
       <c r="AS25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AT25" t="n">
         <v>13</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-14-2013-14</t>
+          <t>2014-01-14</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>6.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AE26" t="n">
         <v>3</v>
@@ -5119,7 +5186,7 @@
         <v>3</v>
       </c>
       <c r="AH26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI26" t="n">
         <v>2</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-14-2013-14</t>
+          <t>2014-01-14</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E27" t="n">
         <v>13</v>
       </c>
       <c r="F27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G27" t="n">
-        <v>0.361</v>
+        <v>0.371</v>
       </c>
       <c r="H27" t="n">
         <v>48.4</v>
@@ -5229,40 +5296,40 @@
         <v>37.5</v>
       </c>
       <c r="J27" t="n">
-        <v>83.7</v>
+        <v>83.5</v>
       </c>
       <c r="K27" t="n">
-        <v>0.448</v>
+        <v>0.449</v>
       </c>
       <c r="L27" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="M27" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="O27" t="n">
         <v>20</v>
       </c>
-      <c r="N27" t="n">
-        <v>0.346</v>
-      </c>
-      <c r="O27" t="n">
-        <v>19.8</v>
-      </c>
       <c r="P27" t="n">
-        <v>25.6</v>
+        <v>25.9</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.771</v>
+        <v>0.775</v>
       </c>
       <c r="R27" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="S27" t="n">
-        <v>31.7</v>
+        <v>31.9</v>
       </c>
       <c r="T27" t="n">
-        <v>43.4</v>
+        <v>43.5</v>
       </c>
       <c r="U27" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="V27" t="n">
         <v>14.7</v>
@@ -5277,28 +5344,28 @@
         <v>5.8</v>
       </c>
       <c r="Z27" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="AA27" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="AB27" t="n">
-        <v>101.7</v>
+        <v>102</v>
       </c>
       <c r="AC27" t="n">
-        <v>-2.3</v>
+        <v>-1.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AE27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF27" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AG27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH27" t="n">
         <v>13</v>
@@ -5313,7 +5380,7 @@
         <v>14</v>
       </c>
       <c r="AL27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM27" t="n">
         <v>21</v>
@@ -5325,7 +5392,7 @@
         <v>5</v>
       </c>
       <c r="AP27" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AQ27" t="n">
         <v>7</v>
@@ -5334,19 +5401,19 @@
         <v>10</v>
       </c>
       <c r="AS27" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT27" t="n">
         <v>12</v>
       </c>
       <c r="AU27" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AV27" t="n">
         <v>12</v>
       </c>
       <c r="AW27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX27" t="n">
         <v>29</v>
@@ -5358,13 +5425,13 @@
         <v>30</v>
       </c>
       <c r="BA27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB27" t="n">
         <v>13</v>
       </c>
       <c r="BC27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-14-2013-14</t>
+          <t>2014-01-14</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5489,7 +5556,7 @@
         <v>1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK28" t="n">
         <v>2</v>
@@ -5519,7 +5586,7 @@
         <v>5</v>
       </c>
       <c r="AT28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU28" t="n">
         <v>2</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-14-2013-14</t>
+          <t>2014-01-14</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>2.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE29" t="n">
         <v>12</v>
@@ -5674,7 +5741,7 @@
         <v>23</v>
       </c>
       <c r="AK29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL29" t="n">
         <v>14</v>
@@ -5683,7 +5750,7 @@
         <v>13</v>
       </c>
       <c r="AN29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO29" t="n">
         <v>7</v>
@@ -5722,7 +5789,7 @@
         <v>28</v>
       </c>
       <c r="BA29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB29" t="n">
         <v>18</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-14-2013-14</t>
+          <t>2014-01-14</t>
         </is>
       </c>
     </row>
@@ -5838,7 +5905,7 @@
         <v>1</v>
       </c>
       <c r="AE30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF30" t="n">
         <v>27</v>
@@ -5868,10 +5935,10 @@
         <v>17</v>
       </c>
       <c r="AO30" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP30" t="n">
         <v>22</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>23</v>
       </c>
       <c r="AQ30" t="n">
         <v>17</v>
@@ -5886,10 +5953,10 @@
         <v>25</v>
       </c>
       <c r="AU30" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV30" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW30" t="n">
         <v>25</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-14-2013-14</t>
+          <t>2014-01-14</t>
         </is>
       </c>
     </row>
@@ -6017,16 +6084,16 @@
         <v>-1.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF31" t="n">
         <v>14</v>
       </c>
       <c r="AG31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH31" t="n">
         <v>4</v>
@@ -6053,10 +6120,10 @@
         <v>27</v>
       </c>
       <c r="AP31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AR31" t="n">
         <v>15</v>
@@ -6071,7 +6138,7 @@
         <v>10</v>
       </c>
       <c r="AV31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW31" t="n">
         <v>9</v>
@@ -6086,7 +6153,7 @@
         <v>14</v>
       </c>
       <c r="BA31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB31" t="n">
         <v>19</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-14-2013-14</t>
+          <t>2014-01-14</t>
         </is>
       </c>
     </row>
